--- a/vse-loti/340834110/spec-340834110.xlsx
+++ b/vse-loti/340834110/spec-340834110.xlsx
@@ -84,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -96,6 +96,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -464,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -557,7 +560,7 @@
         <v>367614.76</v>
       </c>
       <c r="I2" s="5" t="n">
-        <v>441137.71</v>
+        <v>448490.01</v>
       </c>
     </row>
     <row r="3">
@@ -592,7 +595,7 @@
         <v>115877.3</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>139052.76</v>
+        <v>141370.31</v>
       </c>
     </row>
     <row r="4">
@@ -627,7 +630,7 @@
         <v>115877.3</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>139052.76</v>
+        <v>141370.31</v>
       </c>
     </row>
     <row r="5">
@@ -662,7 +665,7 @@
         <v>75993.66</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>91192.39</v>
+        <v>92712.27</v>
       </c>
     </row>
     <row r="6">
@@ -697,7 +700,7 @@
         <v>66760.55</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>80112.66</v>
+        <v>81447.87</v>
       </c>
     </row>
     <row r="7">
@@ -732,7 +735,7 @@
         <v>188081.97</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>225698.36</v>
+        <v>229460</v>
       </c>
     </row>
     <row r="8">
@@ -767,7 +770,7 @@
         <v>109515</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>131418</v>
+        <v>133608.3</v>
       </c>
     </row>
     <row r="9">
@@ -802,7 +805,7 @@
         <v>109515</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>131418</v>
+        <v>133608.3</v>
       </c>
     </row>
     <row r="10">
@@ -837,7 +840,7 @@
         <v>75461.05</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>90553.25999999999</v>
+        <v>92062.48</v>
       </c>
     </row>
     <row r="11">
@@ -872,7 +875,7 @@
         <v>132617.45</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>159140.94</v>
+        <v>161793.29</v>
       </c>
     </row>
     <row r="12">
@@ -907,7 +910,7 @@
         <v>132617.45</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>159140.94</v>
+        <v>161793.29</v>
       </c>
     </row>
     <row r="13">
@@ -942,7 +945,7 @@
         <v>76139</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>91366.8</v>
+        <v>92889.58</v>
       </c>
     </row>
     <row r="14">
@@ -977,7 +980,7 @@
         <v>85226.78</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>102272.14</v>
+        <v>103976.67</v>
       </c>
     </row>
     <row r="15">
@@ -1012,7 +1015,7 @@
         <v>109515</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>131418</v>
+        <v>133608.3</v>
       </c>
     </row>
     <row r="16">
@@ -1038,19 +1041,36 @@
         <v>1278114.61</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>НМЦК с НДС 22% (справочно):</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="n">
+        <v>1559299.82</v>
+      </c>
+    </row>
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
+          <t>Ставка НДС в документах не указана, расчёт справочный по 22 %; суммы источника указаны без НДС: "без НДС" — ТЗ Продукция трубная (ТС) лот 9360828.txt. «без НДС» — сумма из документа, «с НДС» = сумма × 1,22.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
           <t>Источник: Приложение № 1 Спецификация.xlsx
 ТЗ Продукция трубная (ТС) лот 9360828.xlsx</t>
         </is>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A19:B21"/>
+    <mergeCell ref="A21:B23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vse-loti/340834110/spec-340834110.xlsx
+++ b/vse-loti/340834110/spec-340834110.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -479,6 +479,7 @@
     <col width="20.28515625" customWidth="1" min="7" max="7"/>
     <col width="18.85546875" customWidth="1" min="8" max="8"/>
     <col width="16.42578125" customWidth="1" min="9" max="9"/>
+    <col width="18.85546875" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -514,17 +515,22 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Цена за т (без НДС)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Стоимость (без НДС)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Цена за т (без НДС)</t>
-        </is>
-      </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Цена за т (с НДС)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Стоимость (с НДС)</t>
         </is>
       </c>
     </row>
@@ -554,13 +560,16 @@
         <v>0.02</v>
       </c>
       <c r="G2" s="5" t="n">
+        <v>367614.76</v>
+      </c>
+      <c r="H2" s="5" t="n">
         <v>7352.3</v>
-      </c>
-      <c r="H2" s="5" t="n">
-        <v>367614.76</v>
       </c>
       <c r="I2" s="5" t="n">
         <v>448490.01</v>
+      </c>
+      <c r="J2" s="5" t="n">
+        <v>8969.809999999999</v>
       </c>
     </row>
     <row r="3">
@@ -589,13 +598,16 @@
         <v>0.027</v>
       </c>
       <c r="G3" s="5" t="n">
+        <v>115877.3</v>
+      </c>
+      <c r="H3" s="5" t="n">
         <v>3128.69</v>
-      </c>
-      <c r="H3" s="5" t="n">
-        <v>115877.3</v>
       </c>
       <c r="I3" s="5" t="n">
         <v>141370.31</v>
+      </c>
+      <c r="J3" s="5" t="n">
+        <v>3817</v>
       </c>
     </row>
     <row r="4">
@@ -624,13 +636,16 @@
         <v>0.031</v>
       </c>
       <c r="G4" s="5" t="n">
+        <v>115877.3</v>
+      </c>
+      <c r="H4" s="5" t="n">
         <v>3592.19</v>
-      </c>
-      <c r="H4" s="5" t="n">
-        <v>115877.3</v>
       </c>
       <c r="I4" s="5" t="n">
         <v>141370.31</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>4382.47</v>
       </c>
     </row>
     <row r="5">
@@ -659,13 +674,16 @@
         <v>3.958</v>
       </c>
       <c r="G5" s="5" t="n">
+        <v>75993.66</v>
+      </c>
+      <c r="H5" s="5" t="n">
         <v>300782.91</v>
-      </c>
-      <c r="H5" s="5" t="n">
-        <v>75993.66</v>
       </c>
       <c r="I5" s="5" t="n">
         <v>92712.27</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>366955.15</v>
       </c>
     </row>
     <row r="6">
@@ -694,13 +712,16 @@
         <v>2.217</v>
       </c>
       <c r="G6" s="5" t="n">
+        <v>66760.55</v>
+      </c>
+      <c r="H6" s="5" t="n">
         <v>148008.15</v>
-      </c>
-      <c r="H6" s="5" t="n">
-        <v>66760.55</v>
       </c>
       <c r="I6" s="5" t="n">
         <v>81447.87</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>180569.94</v>
       </c>
     </row>
     <row r="7">
@@ -729,13 +750,16 @@
         <v>0.605</v>
       </c>
       <c r="G7" s="5" t="n">
+        <v>188081.97</v>
+      </c>
+      <c r="H7" s="5" t="n">
         <v>113789.59</v>
-      </c>
-      <c r="H7" s="5" t="n">
-        <v>188081.97</v>
       </c>
       <c r="I7" s="5" t="n">
         <v>229460</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>138823.3</v>
       </c>
     </row>
     <row r="8">
@@ -764,13 +788,16 @@
         <v>0.149</v>
       </c>
       <c r="G8" s="5" t="n">
+        <v>109515</v>
+      </c>
+      <c r="H8" s="5" t="n">
         <v>16317.74</v>
-      </c>
-      <c r="H8" s="5" t="n">
-        <v>109515</v>
       </c>
       <c r="I8" s="5" t="n">
         <v>133608.3</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>19907.64</v>
       </c>
     </row>
     <row r="9">
@@ -799,13 +826,16 @@
         <v>0.06</v>
       </c>
       <c r="G9" s="5" t="n">
+        <v>109515</v>
+      </c>
+      <c r="H9" s="5" t="n">
         <v>6570.9</v>
-      </c>
-      <c r="H9" s="5" t="n">
-        <v>109515</v>
       </c>
       <c r="I9" s="5" t="n">
         <v>133608.3</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>8016.5</v>
       </c>
     </row>
     <row r="10">
@@ -834,13 +864,16 @@
         <v>0.05</v>
       </c>
       <c r="G10" s="5" t="n">
+        <v>75461.05</v>
+      </c>
+      <c r="H10" s="5" t="n">
         <v>3773.05</v>
-      </c>
-      <c r="H10" s="5" t="n">
-        <v>75461.05</v>
       </c>
       <c r="I10" s="5" t="n">
         <v>92062.48</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>4603.12</v>
       </c>
     </row>
     <row r="11">
@@ -869,13 +902,16 @@
         <v>0.074</v>
       </c>
       <c r="G11" s="5" t="n">
+        <v>132617.45</v>
+      </c>
+      <c r="H11" s="5" t="n">
         <v>9813.690000000001</v>
-      </c>
-      <c r="H11" s="5" t="n">
-        <v>132617.45</v>
       </c>
       <c r="I11" s="5" t="n">
         <v>161793.29</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>11972.7</v>
       </c>
     </row>
     <row r="12">
@@ -904,13 +940,16 @@
         <v>0.026</v>
       </c>
       <c r="G12" s="5" t="n">
+        <v>132617.45</v>
+      </c>
+      <c r="H12" s="5" t="n">
         <v>3448.05</v>
-      </c>
-      <c r="H12" s="5" t="n">
-        <v>132617.45</v>
       </c>
       <c r="I12" s="5" t="n">
         <v>161793.29</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>4206.62</v>
       </c>
     </row>
     <row r="13">
@@ -939,13 +978,16 @@
         <v>4.944</v>
       </c>
       <c r="G13" s="5" t="n">
+        <v>76139</v>
+      </c>
+      <c r="H13" s="5" t="n">
         <v>376431.22</v>
-      </c>
-      <c r="H13" s="5" t="n">
-        <v>76139</v>
       </c>
       <c r="I13" s="5" t="n">
         <v>92889.58</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>459246.09</v>
       </c>
     </row>
     <row r="14">
@@ -974,13 +1016,16 @@
         <v>3.308</v>
       </c>
       <c r="G14" s="5" t="n">
+        <v>85226.78</v>
+      </c>
+      <c r="H14" s="5" t="n">
         <v>281930.19</v>
-      </c>
-      <c r="H14" s="5" t="n">
-        <v>85226.78</v>
       </c>
       <c r="I14" s="5" t="n">
         <v>103976.67</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>343954.83</v>
       </c>
     </row>
     <row r="15">
@@ -1009,14 +1054,17 @@
         <v>0.029</v>
       </c>
       <c r="G15" s="5" t="n">
+        <v>109515</v>
+      </c>
+      <c r="H15" s="5" t="n">
         <v>3175.94</v>
-      </c>
-      <c r="H15" s="5" t="n">
-        <v>109515</v>
       </c>
       <c r="I15" s="5" t="n">
         <v>133608.3</v>
       </c>
+      <c r="J15" s="5" t="n">
+        <v>3874.65</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -1028,7 +1076,16 @@
         <v>15.498</v>
       </c>
       <c r="G16" s="8" t="n">
+        <v>82469.64999999999</v>
+      </c>
+      <c r="H16" s="8" t="n">
         <v>1278114.61</v>
+      </c>
+      <c r="I16" s="8" t="n">
+        <v>100612.97</v>
+      </c>
+      <c r="J16" s="8" t="n">
+        <v>1559299.82</v>
       </c>
     </row>
     <row r="17">
@@ -1037,7 +1094,7 @@
           <t>НМЦК из обоснования:</t>
         </is>
       </c>
-      <c r="G17" s="8" t="n">
+      <c r="H17" s="8" t="n">
         <v>1278114.61</v>
       </c>
     </row>
@@ -1047,7 +1104,7 @@
           <t>НМЦК с НДС 22% (справочно):</t>
         </is>
       </c>
-      <c r="F18" s="8" t="n">
+      <c r="J18" s="8" t="n">
         <v>1559299.82</v>
       </c>
     </row>
